--- a/app/src/main/res/raw/death_form.xlsx
+++ b/app/src/main/res/raw/death_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -970,7 +970,7 @@
     <t>repeat_name</t>
   </si>
   <si>
-    <t>xml_node_name</t>
+    <t>repeat_xml_node</t>
   </si>
   <si>
     <t>rawDeath</t>
@@ -996,10 +996,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1039,6 +1039,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1046,11 +1054,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1071,17 +1085,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1093,23 +1115,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1124,7 +1131,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1132,7 +1139,38 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1147,44 +1185,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1234,7 +1234,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1246,31 +1336,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1282,19 +1354,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,49 +1366,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1360,13 +1378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1378,31 +1390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1415,6 +1403,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1501,11 +1501,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1521,21 +1527,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1557,30 +1548,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1589,151 +1556,184 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3838,7 +3838,7 @@
     <col min="4" max="4" width="29" customWidth="1"/>
     <col min="5" max="5" width="23.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="11.5428571428571" customWidth="1"/>
-    <col min="7" max="7" width="14.7238095238095" customWidth="1"/>
+    <col min="7" max="7" width="16.7142857142857" customWidth="1"/>
     <col min="8" max="8" width="20.5428571428571" customWidth="1"/>
   </cols>
   <sheetData>

--- a/app/src/main/res/raw/death_form.xlsx
+++ b/app/src/main/res/raw/death_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500"/>
+    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="301">
   <si>
     <t>group</t>
   </si>
@@ -359,9 +359,6 @@
   </si>
   <si>
     <t>start repeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$household_residents </t>
   </si>
   <si>
     <t>5.4. Relationships of Members with the new Head of Household</t>
@@ -998,8 +995,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1061,6 +1058,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1068,9 +1073,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1085,23 +1120,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1116,14 +1165,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1131,58 +1173,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Arial"/>
@@ -1240,55 +1237,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1300,49 +1261,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1354,49 +1273,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1409,6 +1286,126 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1501,32 +1498,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1542,26 +1529,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1589,142 +1556,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2657,20 +2654,18 @@
         <v>91</v>
       </c>
       <c r="F14" s="38"/>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="38"/>
+      <c r="H14" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="I14" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="J14" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="52" t="s">
+      <c r="K14" s="53" t="s">
         <v>95</v>
-      </c>
-      <c r="K14" s="53" t="s">
-        <v>96</v>
       </c>
       <c r="L14" s="54"/>
       <c r="M14" s="54"/>
@@ -2685,25 +2680,25 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
         <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" t="s">
         <v>99</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="46" t="s">
+      <c r="K15" s="47" t="s">
         <v>101</v>
-      </c>
-      <c r="K15" s="47" t="s">
-        <v>102</v>
       </c>
       <c r="L15" s="48"/>
       <c r="M15" s="48"/>
@@ -2716,25 +2711,25 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" t="s">
         <v>104</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="J16" s="46" t="s">
+      <c r="K16" s="47" t="s">
         <v>106</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>107</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -2748,25 +2743,25 @@
     <row r="17" spans="1:14">
       <c r="A17" s="1"/>
       <c r="D17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" t="s">
         <v>108</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="H17" t="s">
         <v>110</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>111</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="J17" s="46" t="s">
+      <c r="K17" s="47" t="s">
         <v>113</v>
-      </c>
-      <c r="K17" s="47" t="s">
-        <v>114</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -2782,7 +2777,7 @@
         <v>90</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
@@ -2799,27 +2794,27 @@
     </row>
     <row r="19" s="26" customFormat="1" spans="1:15">
       <c r="A19" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="E19" s="26" t="s">
         <v>117</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>118</v>
       </c>
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
       <c r="H19" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="J19" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="J19" s="55" t="s">
+      <c r="K19" s="56" t="s">
         <v>121</v>
-      </c>
-      <c r="K19" s="56" t="s">
-        <v>122</v>
       </c>
       <c r="L19" s="57"/>
       <c r="M19" s="57"/>
@@ -2832,27 +2827,27 @@
     </row>
     <row r="20" s="27" customFormat="1" spans="1:15">
       <c r="A20" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>123</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>124</v>
       </c>
       <c r="F20" s="42"/>
       <c r="G20" s="42"/>
       <c r="H20" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="J20" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="J20" s="55" t="s">
+      <c r="K20" s="58" t="s">
         <v>127</v>
-      </c>
-      <c r="K20" s="58" t="s">
-        <v>128</v>
       </c>
       <c r="L20" s="59"/>
       <c r="M20" s="59"/>
@@ -2865,25 +2860,25 @@
     </row>
     <row r="21" s="27" customFormat="1" spans="1:18">
       <c r="A21" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="H21" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="I21" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" s="58" t="s">
         <v>131</v>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K21" s="58" t="s">
-        <v>132</v>
       </c>
       <c r="L21" s="59"/>
       <c r="M21" s="59"/>
@@ -2896,25 +2891,25 @@
     </row>
     <row r="22" s="27" customFormat="1" spans="1:18">
       <c r="A22" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" s="58" t="s">
         <v>134</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K22" s="58" t="s">
-        <v>135</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
@@ -2927,25 +2922,25 @@
     </row>
     <row r="23" s="27" customFormat="1" spans="1:18">
       <c r="A23" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K23" s="58" t="s">
         <v>137</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K23" s="58" t="s">
-        <v>138</v>
       </c>
       <c r="L23" s="59"/>
       <c r="M23" s="59"/>
@@ -2958,10 +2953,10 @@
     </row>
     <row r="24" s="28" customFormat="1" spans="1:15">
       <c r="A24" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>20</v>
@@ -2969,16 +2964,16 @@
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
       <c r="H24" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="J24" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="J24" s="55" t="s">
+      <c r="K24" s="60" t="s">
         <v>142</v>
-      </c>
-      <c r="K24" s="60" t="s">
-        <v>143</v>
       </c>
       <c r="L24" s="61"/>
       <c r="M24" s="61"/>
@@ -3078,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
@@ -3101,19 +3096,19 @@
         <v>68</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>146</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="G2" s="1"/>
     </row>
@@ -3122,265 +3117,265 @@
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
         <v>150</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>151</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>159</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>160</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>164</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>165</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>170</v>
-      </c>
       <c r="G6" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" t="s">
         <v>212</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>213</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3388,19 +3383,19 @@
         <v>44</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3408,19 +3403,19 @@
         <v>44</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3428,19 +3423,19 @@
         <v>44</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3448,19 +3443,19 @@
         <v>44</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3468,19 +3463,19 @@
         <v>44</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="D20" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3488,19 +3483,19 @@
         <v>44</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3508,19 +3503,19 @@
         <v>44</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="D22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="E22" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3528,19 +3523,19 @@
         <v>44</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="D23" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3548,19 +3543,19 @@
         <v>44</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="F24" s="23" t="s">
         <v>255</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>256</v>
       </c>
       <c r="G24" s="14"/>
     </row>
@@ -3569,19 +3564,19 @@
         <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" t="s">
         <v>257</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>258</v>
-      </c>
-      <c r="D25" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>259</v>
       </c>
       <c r="G25" s="14"/>
     </row>
@@ -3590,19 +3585,19 @@
         <v>56</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="F26" s="23" t="s">
         <v>263</v>
-      </c>
-      <c r="F26" s="23" t="s">
-        <v>264</v>
       </c>
       <c r="G26" s="14"/>
     </row>
@@ -3611,19 +3606,19 @@
         <v>56</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="F27" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>269</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -3632,19 +3627,19 @@
         <v>56</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="F28" s="23" t="s">
         <v>273</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>274</v>
       </c>
       <c r="G28" s="14"/>
     </row>
@@ -3653,19 +3648,19 @@
         <v>56</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="D29" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="F29" s="23" t="s">
         <v>278</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>279</v>
       </c>
       <c r="G29" s="14"/>
     </row>
@@ -3674,19 +3669,19 @@
         <v>56</v>
       </c>
       <c r="B30" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="E30" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="F30" s="23" t="s">
         <v>283</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>284</v>
       </c>
       <c r="G30" s="14"/>
     </row>
@@ -3695,19 +3690,19 @@
         <v>56</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>253</v>
-      </c>
       <c r="D31" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="F31" s="23" t="s">
         <v>286</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>287</v>
       </c>
       <c r="G31" s="14"/>
     </row>
@@ -3844,45 +3839,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>289</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>292</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" t="s">
         <v>296</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>297</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -3891,7 +3886,7 @@
         <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/app/src/main/res/raw/death_form.xlsx
+++ b/app/src/main/res/raw/death_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
+    <workbookView windowWidth="27795" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="302">
   <si>
     <t>group</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>start repeat</t>
+  </si>
+  <si>
+    <t>$external</t>
   </si>
   <si>
     <t>5.4. Relationships of Members with the new Head of Household</t>
@@ -994,9 +997,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1059,7 +1062,44 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1074,18 +1114,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1097,15 +1129,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1120,32 +1146,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1165,25 +1176,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1237,7 +1240,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1249,19 +1318,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1273,19 +1360,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1303,55 +1384,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1363,19 +1402,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1387,31 +1414,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1489,31 +1492,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1529,6 +1533,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1550,178 +1563,168 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1801,6 +1804,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1814,7 +1818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1827,13 +1830,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1859,11 +1859,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2199,8 +2202,8 @@
     <col min="3" max="3" width="14.1809523809524" customWidth="1"/>
     <col min="4" max="4" width="20.1809523809524" customWidth="1"/>
     <col min="5" max="5" width="11.7238095238095" customWidth="1"/>
-    <col min="6" max="6" width="13.5428571428571" style="29" customWidth="1"/>
-    <col min="7" max="7" width="20" style="29" customWidth="1"/>
+    <col min="6" max="6" width="13.5428571428571" style="30" customWidth="1"/>
+    <col min="7" max="7" width="20" style="30" customWidth="1"/>
     <col min="8" max="8" width="51.5428571428571" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
     <col min="10" max="10" width="55.8571428571429" customWidth="1"/>
@@ -2228,10 +2231,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2240,7 +2243,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -2258,7 +2261,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -2286,7 +2289,7 @@
       <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -2300,7 +2303,7 @@
       <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="29"/>
+      <c r="P2" s="30"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
@@ -2318,14 +2321,14 @@
       <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="46" t="s">
+      <c r="J3" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
       <c r="N3" t="b">
         <v>1</v>
       </c>
@@ -2349,14 +2352,14 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="J4" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
       <c r="N4" t="b">
         <v>1</v>
       </c>
@@ -2378,14 +2381,14 @@
       <c r="I5" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="46" t="s">
+      <c r="J5" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
       <c r="N5" t="b">
         <v>1</v>
       </c>
@@ -2398,7 +2401,7 @@
       <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>44</v>
       </c>
       <c r="H6" t="s">
@@ -2407,14 +2410,14 @@
       <c r="I6" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
       <c r="N6" t="b">
         <v>1</v>
       </c>
@@ -2433,14 +2436,14 @@
       <c r="I7" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="46" t="s">
+      <c r="J7" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="47" t="s">
+      <c r="K7" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
       <c r="N7" t="b">
         <v>1</v>
       </c>
@@ -2456,7 +2459,7 @@
       <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>56</v>
       </c>
       <c r="H8" t="s">
@@ -2465,14 +2468,14 @@
       <c r="I8" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="46" t="s">
+      <c r="J8" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
       <c r="N8" t="b">
         <v>1</v>
       </c>
@@ -2491,14 +2494,14 @@
       <c r="I9" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="46" t="s">
+      <c r="J9" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
       <c r="N9" t="b">
         <v>1</v>
       </c>
@@ -2514,7 +2517,7 @@
       <c r="E10" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="30" t="s">
         <v>68</v>
       </c>
       <c r="H10" t="s">
@@ -2523,14 +2526,14 @@
       <c r="I10" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
       <c r="N10" t="b">
         <v>1</v>
       </c>
@@ -2539,7 +2542,7 @@
       </c>
     </row>
     <row r="11" s="25" customFormat="1" spans="1:18">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="D11" s="25" t="s">
         <v>73</v>
       </c>
@@ -2556,14 +2559,14 @@
       <c r="I11" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="50" t="s">
+      <c r="K11" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
       <c r="N11" s="25" t="b">
         <v>1</v>
       </c>
@@ -2590,14 +2593,14 @@
       <c r="I12" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
       <c r="N12" t="b">
         <v>1</v>
       </c>
@@ -2618,21 +2621,21 @@
       <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="29"/>
+      <c r="F13" s="30"/>
       <c r="H13" t="s">
         <v>86</v>
       </c>
       <c r="I13" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
       <c r="N13" t="b">
         <v>1</v>
       </c>
@@ -2643,10 +2646,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+    <row r="14" s="26" customFormat="1" spans="1:17">
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="33" t="s">
         <v>90</v>
       </c>
@@ -2654,54 +2657,56 @@
         <v>91</v>
       </c>
       <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39" t="s">
+      <c r="G14" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="H14" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="J14" s="52" t="s">
+      <c r="I14" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="K14" s="53" t="s">
+      <c r="J14" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
+      <c r="K14" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
       <c r="N14" s="39" t="b">
         <v>1</v>
       </c>
       <c r="O14" s="39"/>
-      <c r="P14" s="39" t="s">
+      <c r="P14" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Q14" s="39"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="J15" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
+      <c r="K15" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
       <c r="N15" t="b">
         <v>1</v>
       </c>
@@ -2711,28 +2716,28 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="J16" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
+      <c r="K16" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
       <c r="N16" t="b">
         <v>1</v>
       </c>
@@ -2743,274 +2748,274 @@
     <row r="17" spans="1:14">
       <c r="A17" s="1"/>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="29" t="s">
         <v>109</v>
       </c>
+      <c r="F17" s="30" t="s">
+        <v>110</v>
+      </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
-      </c>
-      <c r="J17" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="J17" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
+      <c r="K17" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
       <c r="N17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="31"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+    <row r="18" s="26" customFormat="1" spans="1:17">
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="33" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
+        <v>115</v>
+      </c>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
       <c r="J18" s="39"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
       <c r="N18" s="39"/>
       <c r="O18" s="39"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="39"/>
     </row>
-    <row r="19" s="26" customFormat="1" spans="1:15">
+    <row r="19" s="27" customFormat="1" spans="1:15">
       <c r="A19" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="D19" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="26" t="s">
+      <c r="E19" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="27" t="s">
         <v>119</v>
       </c>
+      <c r="I19" s="27" t="s">
+        <v>120</v>
+      </c>
       <c r="J19" s="55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K19" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" s="57"/>
       <c r="M19" s="57"/>
-      <c r="N19" s="26" t="b">
+      <c r="N19" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="26" t="b">
+      <c r="O19" s="27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="27" customFormat="1" spans="1:15">
+    <row r="20" s="28" customFormat="1" spans="1:15">
       <c r="A20" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="28" t="s">
         <v>125</v>
       </c>
+      <c r="I20" s="28" t="s">
+        <v>126</v>
+      </c>
       <c r="J20" s="55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K20" s="58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L20" s="59"/>
       <c r="M20" s="59"/>
-      <c r="N20" s="27" t="b">
+      <c r="N20" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="O20" s="27" t="b">
+      <c r="O20" s="28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="27" customFormat="1" spans="1:18">
+    <row r="21" s="28" customFormat="1" spans="1:18">
       <c r="A21" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="27" t="s">
-        <v>130</v>
+      <c r="H21" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K21" s="58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L21" s="59"/>
       <c r="M21" s="59"/>
-      <c r="O21" s="27" t="b">
+      <c r="O21" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="R21" s="27" t="b">
+      <c r="R21" s="28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" s="27" customFormat="1" spans="1:18">
+    <row r="22" s="28" customFormat="1" spans="1:18">
       <c r="A22" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>133</v>
+      <c r="H22" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>134</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K22" s="58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
-      <c r="O22" s="27" t="b">
+      <c r="O22" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="R22" s="27" t="b">
+      <c r="R22" s="28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" s="27" customFormat="1" spans="1:18">
+    <row r="23" s="28" customFormat="1" spans="1:18">
       <c r="A23" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>136</v>
+      <c r="H23" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>137</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K23" s="58" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L23" s="59"/>
       <c r="M23" s="59"/>
-      <c r="O23" s="27" t="b">
+      <c r="O23" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="R23" s="27" t="b">
+      <c r="R23" s="28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" s="28" customFormat="1" spans="1:15">
+    <row r="24" s="29" customFormat="1" spans="1:15">
       <c r="A24" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="I24" s="28" t="s">
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="29" t="s">
         <v>140</v>
       </c>
+      <c r="I24" s="29" t="s">
+        <v>141</v>
+      </c>
       <c r="J24" s="55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K24" s="60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L24" s="61"/>
       <c r="M24" s="61"/>
-      <c r="N24" s="28" t="b">
+      <c r="N24" s="29" t="b">
         <v>1</v>
       </c>
-      <c r="O24" s="28" t="b">
+      <c r="O24" s="29" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1"/>
@@ -3073,7 +3078,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
@@ -3096,19 +3101,19 @@
         <v>68</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G2" s="1"/>
     </row>
@@ -3117,265 +3122,265 @@
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3383,19 +3388,19 @@
         <v>44</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3403,19 +3408,19 @@
         <v>44</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3423,19 +3428,19 @@
         <v>44</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3443,19 +3448,19 @@
         <v>44</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3463,19 +3468,19 @@
         <v>44</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D20" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3483,19 +3488,19 @@
         <v>44</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3503,19 +3508,19 @@
         <v>44</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3523,19 +3528,19 @@
         <v>44</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3543,19 +3548,19 @@
         <v>44</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G24" s="14"/>
     </row>
@@ -3564,19 +3569,19 @@
         <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G25" s="14"/>
     </row>
@@ -3585,19 +3590,19 @@
         <v>56</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G26" s="14"/>
     </row>
@@ -3606,19 +3611,19 @@
         <v>56</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -3627,19 +3632,19 @@
         <v>56</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G28" s="14"/>
     </row>
@@ -3648,19 +3653,19 @@
         <v>56</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G29" s="14"/>
     </row>
@@ -3669,19 +3674,19 @@
         <v>56</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G30" s="14"/>
     </row>
@@ -3690,19 +3695,19 @@
         <v>56</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G31" s="14"/>
     </row>
@@ -3839,45 +3844,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -3886,7 +3891,7 @@
         <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
